--- a/resources/data1.xlsx
+++ b/resources/data1.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="133">
   <si>
     <t>类别</t>
   </si>
@@ -1587,7 +1587,9 @@
       </c>
     </row>
     <row r="3" s="6" customFormat="1" ht="17.4" spans="1:6">
-      <c r="A3" s="5"/>
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
@@ -1605,7 +1607,9 @@
       </c>
     </row>
     <row r="4" s="6" customFormat="1" ht="17.4" spans="1:6">
-      <c r="A4" s="5"/>
+      <c r="A4" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
@@ -1623,7 +1627,9 @@
       </c>
     </row>
     <row r="5" s="6" customFormat="1" ht="17.4" spans="1:6">
-      <c r="A5" s="5"/>
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
@@ -1641,7 +1647,9 @@
       </c>
     </row>
     <row r="6" s="6" customFormat="1" ht="17.4" spans="1:6">
-      <c r="A6" s="5"/>
+      <c r="A6" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="B6" s="5" t="s">
         <v>14</v>
       </c>
@@ -2329,8 +2337,7 @@
       <c r="C51" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A2:A6"/>
+  <mergeCells count="6">
     <mergeCell ref="A7:A10"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A14:A19"/>
